--- a/GV.xlsx
+++ b/GV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FlashProjects\DGNLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\FlashProjects\DGNLS - DT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594A9DE0-1136-41E0-BECE-20546DBA998B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8CE2E4-468D-4A9B-8F4C-A54C1B8DEB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GIAOVIEN" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="266">
   <si>
     <t>MÃ LV</t>
   </si>
@@ -135,9 +135,6 @@
     <t>TENHD</t>
   </si>
   <si>
-    <t>LVI</t>
-  </si>
-  <si>
     <t>KIỂM TRA, ĐÁNH GIÁ</t>
   </si>
   <si>
@@ -300,9 +297,6 @@
     <t>tinthiem</t>
   </si>
   <si>
-    <t>LVII</t>
-  </si>
-  <si>
     <t>Đạt</t>
   </si>
   <si>
@@ -381,9 +375,6 @@
     <t>2c7a9e9d</t>
   </si>
   <si>
-    <t>LVIII</t>
-  </si>
-  <si>
     <t>thanhtrinh2103@gmail.com</t>
   </si>
   <si>
@@ -489,9 +480,6 @@
     <t>TC401</t>
   </si>
   <si>
-    <t>LVIV</t>
-  </si>
-  <si>
     <t>Kiểm tra trực tuyến</t>
   </si>
   <si>
@@ -558,9 +546,6 @@
     <t>TC501</t>
   </si>
   <si>
-    <t>LVV</t>
-  </si>
-  <si>
     <t>ĐỊA LÝ</t>
   </si>
   <si>
@@ -648,9 +633,6 @@
     <t>vubichkimbl@gmail.com</t>
   </si>
   <si>
-    <t>LVVI</t>
-  </si>
-  <si>
     <t>vanlanh</t>
   </si>
   <si>
@@ -696,9 +678,6 @@
     <t>HOÀNG THỊ KIM CHI</t>
   </si>
   <si>
-    <t>LVVII</t>
-  </si>
-  <si>
     <t>hoangchi171@gmail.com</t>
   </si>
   <si>
@@ -747,15 +726,9 @@
     <t>TC801</t>
   </si>
   <si>
-    <t>LVVIII</t>
-  </si>
-  <si>
     <t>lytran</t>
   </si>
   <si>
-    <t>TC801. Sáng kiến/chuyển đổi số</t>
-  </si>
-  <si>
     <t>TRẦN TRUNG TRẬN</t>
   </si>
   <si>
@@ -765,9 +738,6 @@
     <t>ttran771@gmail.com</t>
   </si>
   <si>
-    <t>TC802. Tham gia dự án số</t>
-  </si>
-  <si>
     <t>lythoang</t>
   </si>
   <si>
@@ -880,6 +850,12 @@
   </si>
   <si>
     <t>KTPL</t>
+  </si>
+  <si>
+    <t>Sáng kiến/chuyển đổi số</t>
+  </si>
+  <si>
+    <t>Tham gia dự án số</t>
   </si>
 </sst>
 </file>
@@ -930,9 +906,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -969,21 +943,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1252,744 +1223,741 @@
         <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.2">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.2">
       <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13.2">
       <c r="A6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="13.2">
       <c r="A7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="13.2">
       <c r="A8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="13.2">
       <c r="A9" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="13.2">
       <c r="A10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="13.2">
       <c r="A11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="13.2">
       <c r="A12" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="13.2">
       <c r="A13" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.2">
       <c r="A14" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="13.2">
       <c r="A15" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="13.2">
       <c r="A16" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="13.2">
       <c r="A17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="13.2">
       <c r="A18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="13.2">
       <c r="A19" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="13.2">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="13.2">
       <c r="A21" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="13.2">
       <c r="A22" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="13.2">
       <c r="A23" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="13.2">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="13.2">
       <c r="A25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="13.2">
       <c r="A26" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="13.2">
       <c r="A27" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="13.2">
       <c r="A28" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="13.2">
       <c r="A29" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="13.2">
       <c r="A30" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="13.2">
       <c r="A31" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="13.2">
       <c r="A32" s="1" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="13.2">
       <c r="A33" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="13.2">
       <c r="A34" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="13.2">
       <c r="A35" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="13.2">
       <c r="A36" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="13.2">
       <c r="A37" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="13.2">
       <c r="A38" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{18A91B08-9D90-4980-B445-A311F25497B1}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2041,39 +2009,39 @@
         <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2111,10 +2079,10 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1">
         <v>3</v>
@@ -2122,13 +2090,13 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1">
         <v>3</v>
@@ -2136,13 +2104,13 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -2150,13 +2118,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1">
         <v>3</v>
@@ -2164,13 +2132,13 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -2178,13 +2146,13 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D7" s="1">
         <v>4</v>
@@ -2192,13 +2160,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
@@ -2206,13 +2174,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -2220,13 +2188,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -2234,13 +2202,13 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
@@ -2248,13 +2216,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -2262,13 +2230,13 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -2276,13 +2244,13 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -2290,13 +2258,13 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -2304,13 +2272,13 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -2318,13 +2286,13 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D17" s="1">
         <v>4</v>
@@ -2332,13 +2300,13 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D18" s="1">
         <v>3</v>
@@ -2346,13 +2314,13 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -2360,13 +2328,13 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
@@ -2374,13 +2342,13 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2388,13 +2356,13 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D22" s="1">
         <v>4</v>
@@ -2402,13 +2370,13 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -2416,13 +2384,13 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
@@ -2430,13 +2398,13 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -2444,13 +2412,13 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -2458,13 +2426,13 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -2472,13 +2440,13 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -2486,13 +2454,13 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -2500,13 +2468,13 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>196</v>
+        <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -2514,13 +2482,13 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -2528,13 +2496,13 @@
     </row>
     <row r="32" spans="1:4" ht="16.8">
       <c r="A32" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2542,13 +2510,13 @@
     </row>
     <row r="33" spans="1:4" ht="16.8">
       <c r="A33" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -2556,13 +2524,13 @@
     </row>
     <row r="34" spans="1:4" ht="16.8">
       <c r="A34" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
@@ -2570,13 +2538,13 @@
     </row>
     <row r="35" spans="1:4" ht="16.8">
       <c r="A35" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
@@ -2584,19 +2552,20 @@
     </row>
     <row r="36" spans="1:4" ht="16.8">
       <c r="A36" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>229</v>
+        <v>48</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2632,30 +2601,30 @@
         <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>21</v>
@@ -2664,16 +2633,16 @@
         <v>46225</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="4">
         <v>46226</v>
@@ -2681,28 +2650,28 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4">
         <v>46225</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" s="4">
         <v>46225</v>
@@ -2710,28 +2679,28 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="D4" s="4">
         <v>46226</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" s="4">
         <v>46226</v>
@@ -2739,22 +2708,22 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="4">
         <v>46226</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J5" s="4">
         <v>46226</v>
@@ -2762,28 +2731,28 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D6" s="4">
         <v>46226</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2801,12 +2770,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -2832,22 +2801,22 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
